--- a/Letter Z Model data.xlsx
+++ b/Letter Z Model data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\Ra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\letter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14622BE3-F82E-4C11-9B95-E893983947D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C337A194-9309-4BD2-9958-A202160DE74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Y</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>Back Face (Index) List</t>
+  </si>
+  <si>
+    <t>2D vertices</t>
+  </si>
+  <si>
+    <t>3D Vertices</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -290,8 +302,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95520</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -310,7 +322,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -355,8 +367,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>114372</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -375,7 +387,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -420,8 +432,8 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>134172</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -440,7 +452,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -480,8 +492,8 @@
       <xdr:rowOff>95160</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="360" cy="360"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -500,7 +512,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -540,8 +552,8 @@
       <xdr:rowOff>83772</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="59400" cy="30600"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -560,7 +572,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -600,8 +612,8 @@
       <xdr:rowOff>67212</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="56520" cy="66960"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Ink 6">
@@ -620,7 +632,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Ink 6">
@@ -654,23 +666,23 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>85726</xdr:colOff>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>63618</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>53</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>159622</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28954</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
+        <xdr:cNvPr id="14" name="Picture 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCA4A0B-C91C-B035-8589-5D55056B7519}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A63D225C-7189-DC97-65F3-3A20FEFB4616}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -686,8 +698,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8658226" y="2514600"/>
-          <a:ext cx="1533524" cy="1674097"/>
+          <a:off x="8420101" y="2511543"/>
+          <a:ext cx="1800224" cy="1698886"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>120283</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>9904</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02107757-5B5F-21B6-542C-6FB8E426FC28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12696826" y="4248150"/>
+          <a:ext cx="2130057" cy="2010154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1184,13 +1240,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BC2F73-FC1F-461C-AE64-7E2CBDBF257A}">
-  <dimension ref="X5:CI31"/>
+  <dimension ref="X4:CI31"/>
   <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="46" max="46" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="2.875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
+    <col min="61" max="61" width="3.125" customWidth="1"/>
+    <col min="69" max="70" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="4" spans="29:85">
+      <c r="AX4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="5" spans="29:85" ht="15" thickBot="1">
       <c r="AU5" s="6"/>
       <c r="AV5" s="6"/>
@@ -1212,6 +1280,15 @@
       <c r="BH5" s="6"/>
       <c r="BI5" s="6"/>
       <c r="BJ5" s="6"/>
+      <c r="BK5" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="29:85" ht="15" thickBot="1">
       <c r="AD6" s="1"/>
@@ -1240,8 +1317,20 @@
       <c r="BF6" s="6"/>
       <c r="BG6" s="6"/>
       <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
+      <c r="BI6" s="7">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="7"/>
+      <c r="BK6" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BL6" s="7"/>
+      <c r="BM6" s="6">
+        <v>3</v>
+      </c>
+      <c r="BO6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="29:85" ht="15" thickBot="1">
       <c r="AI7" s="5"/>
@@ -1265,8 +1354,20 @@
       <c r="BF7" s="6"/>
       <c r="BG7" s="6"/>
       <c r="BH7" s="6"/>
-      <c r="BI7" s="6"/>
-      <c r="BJ7" s="6"/>
+      <c r="BI7" s="7">
+        <v>1</v>
+      </c>
+      <c r="BJ7" s="7"/>
+      <c r="BK7" s="7">
+        <v>3</v>
+      </c>
+      <c r="BL7" s="7"/>
+      <c r="BM7" s="6">
+        <v>3</v>
+      </c>
+      <c r="BO7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="29:85" ht="15" thickBot="1">
       <c r="AH8" s="5"/>
@@ -1290,8 +1391,20 @@
       <c r="BF8" s="6"/>
       <c r="BG8" s="6"/>
       <c r="BH8" s="6"/>
-      <c r="BI8" s="6"/>
-      <c r="BJ8" s="6"/>
+      <c r="BI8" s="7">
+        <v>2</v>
+      </c>
+      <c r="BJ8" s="7"/>
+      <c r="BK8" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BL8" s="7"/>
+      <c r="BM8" s="6">
+        <v>2</v>
+      </c>
+      <c r="BO8">
+        <v>1</v>
+      </c>
       <c r="BZ8" s="6"/>
       <c r="CA8" s="6"/>
       <c r="CB8" s="6"/>
@@ -1323,8 +1436,20 @@
       <c r="BF9" s="6"/>
       <c r="BG9" s="6"/>
       <c r="BH9" s="6"/>
-      <c r="BI9" s="6"/>
-      <c r="BJ9" s="6"/>
+      <c r="BI9" s="7">
+        <v>3</v>
+      </c>
+      <c r="BJ9" s="7"/>
+      <c r="BK9" s="7">
+        <v>1</v>
+      </c>
+      <c r="BL9" s="7"/>
+      <c r="BM9" s="7">
+        <v>2</v>
+      </c>
+      <c r="BO9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="29:85" ht="15.75" thickTop="1" thickBot="1">
       <c r="AF10" s="5"/>
@@ -1348,8 +1473,20 @@
       <c r="BF10" s="6"/>
       <c r="BG10" s="6"/>
       <c r="BH10" s="6"/>
-      <c r="BI10" s="6"/>
-      <c r="BJ10" s="6"/>
+      <c r="BI10" s="7">
+        <v>4</v>
+      </c>
+      <c r="BJ10" s="7"/>
+      <c r="BK10" s="7">
+        <v>-1</v>
+      </c>
+      <c r="BL10" s="7"/>
+      <c r="BM10" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BO10">
+        <v>1</v>
+      </c>
       <c r="CB10" s="8"/>
       <c r="CC10" s="9"/>
       <c r="CD10" s="9"/>
@@ -1379,8 +1516,20 @@
       <c r="BF11" s="6"/>
       <c r="BG11" s="6"/>
       <c r="BH11" s="6"/>
-      <c r="BI11" s="6"/>
-      <c r="BJ11" s="6"/>
+      <c r="BI11" s="7">
+        <v>5</v>
+      </c>
+      <c r="BJ11" s="7"/>
+      <c r="BK11" s="7">
+        <v>2</v>
+      </c>
+      <c r="BL11" s="7"/>
+      <c r="BM11" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BO11">
+        <v>1</v>
+      </c>
       <c r="CE11" s="14"/>
       <c r="CF11" s="14"/>
     </row>
@@ -1406,8 +1555,20 @@
       <c r="BF12" s="6"/>
       <c r="BG12" s="6"/>
       <c r="BH12" s="6"/>
-      <c r="BI12" s="6"/>
-      <c r="BJ12" s="6"/>
+      <c r="BI12" s="7">
+        <v>6</v>
+      </c>
+      <c r="BJ12" s="7"/>
+      <c r="BK12" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BL12" s="7"/>
+      <c r="BM12" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BO12">
+        <v>1</v>
+      </c>
       <c r="CD12" s="14"/>
       <c r="CE12" s="14"/>
     </row>
@@ -1438,8 +1599,20 @@
       <c r="BF13" s="6"/>
       <c r="BG13" s="6"/>
       <c r="BH13" s="6"/>
-      <c r="BI13" s="6"/>
-      <c r="BJ13" s="6"/>
+      <c r="BI13" s="7">
+        <v>7</v>
+      </c>
+      <c r="BJ13" s="7"/>
+      <c r="BK13" s="7">
+        <v>3</v>
+      </c>
+      <c r="BL13" s="7"/>
+      <c r="BM13" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BO13">
+        <v>1</v>
+      </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="8"/>
     </row>
@@ -1458,8 +1631,20 @@
       <c r="BF14" s="6"/>
       <c r="BG14" s="6"/>
       <c r="BH14" s="6"/>
-      <c r="BI14" s="6"/>
+      <c r="BI14" s="7">
+        <v>8</v>
+      </c>
       <c r="BJ14" s="6"/>
+      <c r="BK14" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BL14" s="7"/>
+      <c r="BM14" s="6">
+        <v>3</v>
+      </c>
+      <c r="BO14">
+        <v>-1</v>
+      </c>
       <c r="CB14" s="8"/>
       <c r="CC14" s="12"/>
       <c r="CD14" s="12"/>
@@ -1482,8 +1667,20 @@
       <c r="BF15" s="6"/>
       <c r="BG15" s="6"/>
       <c r="BH15" s="6"/>
-      <c r="BI15" s="6"/>
+      <c r="BI15" s="7">
+        <v>9</v>
+      </c>
       <c r="BJ15" s="6"/>
+      <c r="BK15" s="7">
+        <v>3</v>
+      </c>
+      <c r="BL15" s="7"/>
+      <c r="BM15" s="6">
+        <v>3</v>
+      </c>
+      <c r="BO15">
+        <v>-1</v>
+      </c>
       <c r="CB15" s="6"/>
       <c r="CC15" s="6"/>
       <c r="CD15" s="6"/>
@@ -1512,10 +1709,22 @@
       <c r="BF16" s="6"/>
       <c r="BG16" s="6"/>
       <c r="BH16" s="6"/>
-      <c r="BI16" s="6"/>
+      <c r="BI16" s="7">
+        <v>10</v>
+      </c>
       <c r="BJ16" s="6"/>
-    </row>
-    <row r="17" spans="24:87" ht="16.5" thickTop="1" thickBot="1">
+      <c r="BK16" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BL16" s="7"/>
+      <c r="BM16" s="6">
+        <v>2</v>
+      </c>
+      <c r="BO16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
       <c r="AB17">
         <v>2</v>
       </c>
@@ -1539,10 +1748,22 @@
       <c r="BF17" s="6"/>
       <c r="BG17" s="6"/>
       <c r="BH17" s="6"/>
-      <c r="BI17" s="6"/>
+      <c r="BI17" s="7">
+        <v>11</v>
+      </c>
       <c r="BJ17" s="6"/>
-    </row>
-    <row r="18" spans="24:87" ht="15.75" thickTop="1">
+      <c r="BK17" s="7">
+        <v>1</v>
+      </c>
+      <c r="BL17" s="7"/>
+      <c r="BM17" s="7">
+        <v>2</v>
+      </c>
+      <c r="BO17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="24:87" ht="15" thickTop="1">
       <c r="AC18" s="19"/>
       <c r="AD18" s="19"/>
       <c r="AE18" s="19">
@@ -1565,10 +1786,22 @@
       <c r="BF18" s="6"/>
       <c r="BG18" s="6"/>
       <c r="BH18" s="6"/>
-      <c r="BI18" s="6"/>
+      <c r="BI18" s="7">
+        <v>12</v>
+      </c>
       <c r="BJ18" s="6"/>
-    </row>
-    <row r="19" spans="24:87" ht="15">
+      <c r="BK18" s="7">
+        <v>-1</v>
+      </c>
+      <c r="BL18" s="7"/>
+      <c r="BM18" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BO18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="24:87">
       <c r="AC19" s="19"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="20"/>
@@ -1589,10 +1822,22 @@
       <c r="BF19" s="6"/>
       <c r="BG19" s="6"/>
       <c r="BH19" s="6"/>
-      <c r="BI19" s="6"/>
+      <c r="BI19" s="7">
+        <v>13</v>
+      </c>
       <c r="BJ19" s="6"/>
-    </row>
-    <row r="20" spans="24:87" ht="15.75" thickBot="1">
+      <c r="BK19" s="7">
+        <v>2</v>
+      </c>
+      <c r="BL19" s="7"/>
+      <c r="BM19" s="7">
+        <v>-2</v>
+      </c>
+      <c r="BO19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="24:87" ht="15" thickBot="1">
       <c r="AC20" s="19"/>
       <c r="AD20" s="20"/>
       <c r="AE20" s="15"/>
@@ -1604,6 +1849,19 @@
         <v>5</v>
       </c>
       <c r="AX20" s="7"/>
+      <c r="BI20" s="7">
+        <v>14</v>
+      </c>
+      <c r="BK20" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BL20" s="7"/>
+      <c r="BM20" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BO20">
+        <v>-1</v>
+      </c>
     </row>
     <row r="21" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
       <c r="AB21">
@@ -1619,6 +1877,19 @@
         <v>7</v>
       </c>
       <c r="AX21" s="7"/>
+      <c r="BI21" s="7">
+        <v>15</v>
+      </c>
+      <c r="BK21" s="7">
+        <v>3</v>
+      </c>
+      <c r="BL21" s="7"/>
+      <c r="BM21" s="7">
+        <v>-3</v>
+      </c>
+      <c r="BO21">
+        <v>-1</v>
+      </c>
     </row>
     <row r="22" spans="24:87" ht="15" thickTop="1">
       <c r="AC22" s="6"/>
@@ -1661,7 +1932,7 @@
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC24" s="6"/>
       <c r="AD24" s="6"/>
@@ -1672,6 +1943,15 @@
       <c r="AT24">
         <v>6</v>
       </c>
+      <c r="AV24">
+        <v>8</v>
+      </c>
+      <c r="AW24">
+        <v>11</v>
+      </c>
+      <c r="AX24">
+        <v>10</v>
+      </c>
       <c r="CB24">
         <v>2</v>
       </c>
@@ -1690,13 +1970,22 @@
         <v>0</v>
       </c>
       <c r="AA25">
+        <v>3</v>
+      </c>
+      <c r="AB25">
         <v>1</v>
-      </c>
-      <c r="AB25">
-        <v>3</v>
       </c>
       <c r="AT25">
         <v>7</v>
+      </c>
+      <c r="AV25">
+        <v>8</v>
+      </c>
+      <c r="AW25">
+        <v>9</v>
+      </c>
+      <c r="AX25">
+        <v>11</v>
       </c>
       <c r="CE25">
         <v>3</v>
@@ -1720,6 +2009,15 @@
       <c r="AT26">
         <v>8</v>
       </c>
+      <c r="AV26">
+        <v>9</v>
+      </c>
+      <c r="AW26">
+        <v>12</v>
+      </c>
+      <c r="AX26">
+        <v>11</v>
+      </c>
       <c r="CE26" s="14"/>
       <c r="CF26" s="14"/>
     </row>
@@ -1731,13 +2029,22 @@
         <v>3</v>
       </c>
       <c r="AA27">
+        <v>6</v>
+      </c>
+      <c r="AB27">
         <v>4</v>
-      </c>
-      <c r="AB27">
-        <v>6</v>
       </c>
       <c r="AT27">
         <v>9</v>
+      </c>
+      <c r="AV27">
+        <v>11</v>
+      </c>
+      <c r="AW27">
+        <v>12</v>
+      </c>
+      <c r="AX27">
+        <v>14</v>
       </c>
       <c r="CD27" s="14"/>
       <c r="CE27" s="8"/>
@@ -1763,6 +2070,15 @@
       </c>
       <c r="AT28">
         <v>10</v>
+      </c>
+      <c r="AV28">
+        <v>12</v>
+      </c>
+      <c r="AW28">
+        <v>15</v>
+      </c>
+      <c r="AX28">
+        <v>14</v>
       </c>
       <c r="CB28">
         <v>6</v>
@@ -1793,6 +2109,15 @@
       <c r="AT29">
         <v>11</v>
       </c>
+      <c r="AV29">
+        <v>12</v>
+      </c>
+      <c r="AW29">
+        <v>13</v>
+      </c>
+      <c r="AX29">
+        <v>15</v>
+      </c>
       <c r="CC29" s="6"/>
       <c r="CD29" s="6"/>
       <c r="CE29" s="6"/>

--- a/Letter Z Model data.xlsx
+++ b/Letter Z Model data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\letter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\let\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C337A194-9309-4BD2-9958-A202160DE74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913B356B-E4C9-4A02-9F52-C32D2203274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Y</t>
   </si>
@@ -64,12 +64,33 @@
   <si>
     <t>x</t>
   </si>
+  <si>
+    <t>2D Texture Vertices</t>
+  </si>
+  <si>
+    <t>Px</t>
+  </si>
+  <si>
+    <t>Py</t>
+  </si>
+  <si>
+    <t>Bottom Face</t>
+  </si>
+  <si>
+    <t>Top Face</t>
+  </si>
+  <si>
+    <t>Side Back face</t>
+  </si>
+  <si>
+    <t>Side Front Face</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,15 +267,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -262,14 +281,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -298,7 +316,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>300</xdr:colOff>
+      <xdr:colOff>299</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95520</xdr:rowOff>
     </xdr:to>
@@ -363,7 +381,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>36660</xdr:colOff>
+      <xdr:colOff>36659</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>114372</xdr:rowOff>
     </xdr:to>
@@ -428,7 +446,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>33780</xdr:colOff>
+      <xdr:colOff>33779</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>134172</xdr:rowOff>
     </xdr:to>
@@ -486,9 +504,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>82</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>190440</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>95160</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="360" cy="360"/>
@@ -546,9 +564,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>82</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>167760</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>83772</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="59400" cy="30600"/>
@@ -606,9 +624,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>82</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>167760</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>67212</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="56520" cy="66960"/>
@@ -672,10 +690,10 @@
       <xdr:rowOff>63618</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>53</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>28954</xdr:rowOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>87474</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>194183</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -710,16 +728,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>65</xdr:col>
-      <xdr:colOff>142876</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>103997</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>105552</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>120283</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>9904</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>139721</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>126536</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -742,8 +760,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12696826" y="4248150"/>
-          <a:ext cx="2130057" cy="2010154"/>
+          <a:off x="1095375" y="5062440"/>
+          <a:ext cx="1853249" cy="2159249"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>58316</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>113328</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>55784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9041958-0916-4D57-37DA-84F3081E1D02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3110204" y="7347857"/>
+          <a:ext cx="9754961" cy="9716856"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -807,7 +869,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'3'0'0,"0"2"0,3 2 0,3-1 0,0 3 0,1-1 0,1 0 0,2 1 0,1-1 0,-2 3 0,0-2 0,1 0 0,-3 0 0,1 0 0,0-2 0,-1 2 0,-3 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'2'0'0,"0"2"0,2 2 0,2-1 0,1 3 0,-1-1 0,2 0 0,1 1 0,0-1 0,0 3 0,-1-2 0,1 0 0,-2 0 0,0 0 0,1-2 0,-1 2 0,-3 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -835,7 +897,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">157 0 24575,'0'5'0,"0"0"0,-1 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,-1 1 0,-2 3 0,-3 1 0,1-1 0,-1 0 0,0-1 0,-13 9 0,-3 4 0,7-5 1,-16 13-1367,23-24-5460</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">104 0 24575,'0'5'0,"0"0"0,0 0 0,0 0 0,-1 0 0,0-1 0,1 1 0,-2 0 0,2 0 0,-2-1 0,1 1 0,0-1 0,-1 1 0,-2 3 0,-1 1 0,0-1 0,0 0 0,0-1 0,-9 9 0,-2 4 0,5-5 1,-11 13-1367,15-24-5460</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1240,46 +1302,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BC2F73-FC1F-461C-AE64-7E2CBDBF257A}">
-  <dimension ref="X4:CI31"/>
-  <sheetFormatPr defaultColWidth="2.5" defaultRowHeight="14.25"/>
+  <dimension ref="J4:BV34"/>
+  <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="46" max="46" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="3" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="3" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
-    <col min="61" max="61" width="3.125" customWidth="1"/>
-    <col min="69" max="70" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="3" bestFit="1" customWidth="1"/>
+    <col min="54" max="56" width="2.85546875" customWidth="1"/>
+    <col min="61" max="61" width="3.140625" customWidth="1"/>
+    <col min="69" max="70" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="29:85">
+    <row r="4" spans="10:74" x14ac:dyDescent="0.25">
       <c r="AX4" t="s">
         <v>4</v>
       </c>
       <c r="BI4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="29:85" ht="15" thickBot="1">
-      <c r="AU5" s="6"/>
-      <c r="AV5" s="6"/>
-      <c r="AW5" s="6"/>
-      <c r="AX5" s="6"/>
-      <c r="AY5" s="6"/>
-      <c r="AZ5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="6"/>
-      <c r="BB5" s="6" t="s">
+      <c r="BR4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AZ5" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="s">
         <v>0</v>
       </c>
-      <c r="BC5" s="6"/>
-      <c r="BD5" s="6"/>
-      <c r="BE5" s="6"/>
-      <c r="BF5" s="6"/>
-      <c r="BG5" s="6"/>
-      <c r="BH5" s="6"/>
-      <c r="BI5" s="6"/>
-      <c r="BJ5" s="6"/>
       <c r="BK5" t="s">
         <v>7</v>
       </c>
@@ -1289,640 +1350,531 @@
       <c r="BO5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="29:85" ht="15" thickBot="1">
+      <c r="BT5" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AD6" s="1"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
       <c r="AG6" s="2"/>
       <c r="AH6" s="2"/>
       <c r="AI6" s="3"/>
-      <c r="AU6" s="6"/>
-      <c r="AV6" s="7"/>
-      <c r="AW6" s="7"/>
-      <c r="AX6" s="7">
+      <c r="AX6">
         <v>0</v>
       </c>
-      <c r="AY6" s="7"/>
-      <c r="AZ6" s="7">
+      <c r="AZ6">
         <v>-2</v>
       </c>
-      <c r="BA6" s="7"/>
-      <c r="BB6" s="6">
-        <v>3</v>
-      </c>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
-      <c r="BF6" s="6"/>
-      <c r="BG6" s="6"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="7">
+      <c r="BB6">
+        <v>3</v>
+      </c>
+      <c r="BI6">
         <v>0</v>
       </c>
-      <c r="BJ6" s="7"/>
-      <c r="BK6" s="7">
+      <c r="BK6">
         <v>-2</v>
       </c>
-      <c r="BL6" s="7"/>
-      <c r="BM6" s="6">
+      <c r="BM6">
         <v>3</v>
       </c>
       <c r="BO6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="29:85" ht="15" thickBot="1">
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>98</v>
+      </c>
+      <c r="BV6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AI7" s="5"/>
-      <c r="AU7" s="6"/>
-      <c r="AV7" s="7"/>
-      <c r="AW7" s="7"/>
-      <c r="AX7" s="7">
-        <v>1</v>
-      </c>
-      <c r="AY7" s="7"/>
-      <c r="AZ7" s="7">
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
         <v>2</v>
       </c>
-      <c r="BA7" s="7"/>
-      <c r="BB7" s="6">
-        <v>3</v>
-      </c>
-      <c r="BC7" s="6"/>
-      <c r="BD7" s="6"/>
-      <c r="BE7" s="6"/>
-      <c r="BF7" s="6"/>
-      <c r="BG7" s="6"/>
-      <c r="BH7" s="6"/>
-      <c r="BI7" s="7">
-        <v>1</v>
-      </c>
-      <c r="BJ7" s="7"/>
-      <c r="BK7" s="7">
-        <v>3</v>
-      </c>
-      <c r="BL7" s="7"/>
-      <c r="BM7" s="6">
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BI7">
+        <v>1</v>
+      </c>
+      <c r="BK7">
+        <v>3</v>
+      </c>
+      <c r="BM7">
         <v>3</v>
       </c>
       <c r="BO7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="29:85" ht="15" thickBot="1">
+      <c r="BR7">
+        <v>1</v>
+      </c>
+      <c r="BT7">
+        <v>349</v>
+      </c>
+      <c r="BV7">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AH8" s="5"/>
-      <c r="AU8" s="6"/>
-      <c r="AV8" s="7"/>
-      <c r="AW8" s="7"/>
-      <c r="AX8" s="7">
+      <c r="AX8">
         <v>2</v>
       </c>
-      <c r="AY8" s="7"/>
-      <c r="AZ8" s="7">
+      <c r="AZ8">
         <v>-3</v>
       </c>
-      <c r="BA8" s="7"/>
-      <c r="BB8" s="6">
+      <c r="BB8">
         <v>2</v>
       </c>
-      <c r="BC8" s="6"/>
-      <c r="BD8" s="6"/>
-      <c r="BE8" s="6"/>
-      <c r="BF8" s="6"/>
-      <c r="BG8" s="6"/>
-      <c r="BH8" s="6"/>
-      <c r="BI8" s="7">
+      <c r="BI8">
         <v>2</v>
       </c>
-      <c r="BJ8" s="7"/>
-      <c r="BK8" s="7">
+      <c r="BK8">
         <v>-3</v>
       </c>
-      <c r="BL8" s="7"/>
-      <c r="BM8" s="6">
+      <c r="BM8">
         <v>2</v>
       </c>
       <c r="BO8">
         <v>1</v>
       </c>
-      <c r="BZ8" s="6"/>
-      <c r="CA8" s="6"/>
-      <c r="CB8" s="6"/>
-      <c r="CC8" s="6"/>
-      <c r="CD8" s="6"/>
-      <c r="CE8" s="6"/>
-      <c r="CF8" s="6"/>
-      <c r="CG8" s="6"/>
-    </row>
-    <row r="9" spans="29:85" ht="15" thickBot="1">
+      <c r="BR8">
+        <v>2</v>
+      </c>
+      <c r="BT8">
+        <v>554</v>
+      </c>
+      <c r="BV8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
       <c r="AG9" s="5"/>
-      <c r="AU9" s="6"/>
-      <c r="AV9" s="7"/>
-      <c r="AW9" s="7"/>
-      <c r="AX9" s="7">
-        <v>3</v>
-      </c>
-      <c r="AY9" s="7"/>
-      <c r="AZ9" s="7">
-        <v>1</v>
-      </c>
-      <c r="BA9" s="7"/>
-      <c r="BB9" s="7">
+      <c r="AX9">
+        <v>3</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
+      <c r="BB9">
         <v>2</v>
       </c>
-      <c r="BC9" s="6"/>
-      <c r="BD9" s="6"/>
-      <c r="BE9" s="6"/>
-      <c r="BF9" s="6"/>
-      <c r="BG9" s="6"/>
-      <c r="BH9" s="6"/>
-      <c r="BI9" s="7">
-        <v>3</v>
-      </c>
-      <c r="BJ9" s="7"/>
-      <c r="BK9" s="7">
-        <v>1</v>
-      </c>
-      <c r="BL9" s="7"/>
-      <c r="BM9" s="7">
+      <c r="BI9">
+        <v>3</v>
+      </c>
+      <c r="BK9">
+        <v>1</v>
+      </c>
+      <c r="BM9">
         <v>2</v>
       </c>
       <c r="BO9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="29:85" ht="15.75" thickTop="1" thickBot="1">
+      <c r="BR9">
+        <v>3</v>
+      </c>
+      <c r="BT9">
+        <v>804</v>
+      </c>
+      <c r="BV9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="9"/>
       <c r="AF10" s="5"/>
-      <c r="AU10" s="6"/>
-      <c r="AV10" s="7"/>
-      <c r="AW10" s="7"/>
-      <c r="AX10" s="7">
+      <c r="AX10">
         <v>4</v>
       </c>
-      <c r="AY10" s="7"/>
-      <c r="AZ10" s="7">
-        <v>1</v>
-      </c>
-      <c r="BA10" s="7"/>
-      <c r="BB10" s="7">
+      <c r="AZ10">
+        <v>1</v>
+      </c>
+      <c r="BB10">
         <v>-1</v>
       </c>
-      <c r="BC10" s="6"/>
-      <c r="BD10" s="6"/>
-      <c r="BE10" s="6"/>
-      <c r="BF10" s="6"/>
-      <c r="BG10" s="6"/>
-      <c r="BH10" s="6"/>
-      <c r="BI10" s="7">
+      <c r="BI10">
         <v>4</v>
       </c>
-      <c r="BJ10" s="7"/>
-      <c r="BK10" s="7">
+      <c r="BK10">
         <v>-1</v>
       </c>
-      <c r="BL10" s="7"/>
-      <c r="BM10" s="7">
+      <c r="BM10">
         <v>-2</v>
       </c>
       <c r="BO10">
         <v>1</v>
       </c>
-      <c r="CB10" s="8"/>
-      <c r="CC10" s="9"/>
-      <c r="CD10" s="9"/>
-      <c r="CE10" s="9"/>
-      <c r="CF10" s="10"/>
-      <c r="CG10" s="11"/>
-    </row>
-    <row r="11" spans="29:85" ht="15" thickBot="1">
+      <c r="BR10">
+        <v>4</v>
+      </c>
+      <c r="BT10">
+        <v>207</v>
+      </c>
+      <c r="BV10">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
       <c r="AE11" s="5"/>
-      <c r="AU11" s="6"/>
-      <c r="AV11" s="7"/>
-      <c r="AW11" s="7"/>
-      <c r="AX11" s="7">
+      <c r="AX11">
         <v>5</v>
       </c>
-      <c r="AY11" s="7"/>
-      <c r="AZ11" s="7">
+      <c r="AZ11">
         <v>2</v>
       </c>
-      <c r="BA11" s="7"/>
-      <c r="BB11" s="7">
+      <c r="BB11">
         <v>-1</v>
       </c>
-      <c r="BC11" s="6"/>
-      <c r="BD11" s="6"/>
-      <c r="BE11" s="6"/>
-      <c r="BF11" s="6"/>
-      <c r="BG11" s="6"/>
-      <c r="BH11" s="6"/>
-      <c r="BI11" s="7">
+      <c r="BI11">
         <v>5</v>
       </c>
-      <c r="BJ11" s="7"/>
-      <c r="BK11" s="7">
+      <c r="BK11">
         <v>2</v>
       </c>
-      <c r="BL11" s="7"/>
-      <c r="BM11" s="7">
+      <c r="BM11">
         <v>-2</v>
       </c>
       <c r="BO11">
         <v>1</v>
       </c>
-      <c r="CE11" s="14"/>
-      <c r="CF11" s="14"/>
-    </row>
-    <row r="12" spans="29:85" ht="15" thickBot="1">
+      <c r="BR11">
+        <v>5</v>
+      </c>
+      <c r="BT11">
+        <v>297</v>
+      </c>
+      <c r="BV11">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
       <c r="AD12" s="4"/>
-      <c r="AU12" s="6"/>
-      <c r="AV12" s="7"/>
-      <c r="AW12" s="7"/>
-      <c r="AX12" s="7">
+      <c r="AX12">
         <v>6</v>
       </c>
-      <c r="AY12" s="7"/>
-      <c r="AZ12" s="7">
+      <c r="AZ12">
         <v>-3</v>
       </c>
-      <c r="BA12" s="7"/>
-      <c r="BB12" s="7">
+      <c r="BB12">
         <v>-2</v>
       </c>
-      <c r="BC12" s="6"/>
-      <c r="BD12" s="6"/>
-      <c r="BE12" s="6"/>
-      <c r="BF12" s="6"/>
-      <c r="BG12" s="6"/>
-      <c r="BH12" s="6"/>
-      <c r="BI12" s="7">
+      <c r="BI12">
         <v>6</v>
       </c>
-      <c r="BJ12" s="7"/>
-      <c r="BK12" s="7">
+      <c r="BK12">
         <v>-3</v>
       </c>
-      <c r="BL12" s="7"/>
-      <c r="BM12" s="7">
+      <c r="BM12">
         <v>-3</v>
       </c>
       <c r="BO12">
         <v>1</v>
       </c>
-      <c r="CD12" s="14"/>
-      <c r="CE12" s="14"/>
-    </row>
-    <row r="13" spans="29:85" ht="15" thickBot="1">
+      <c r="BR12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="12"/>
+      <c r="M13" s="6"/>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="P13">
+        <v>5</v>
+      </c>
       <c r="AD13" s="1"/>
       <c r="AE13" s="2"/>
       <c r="AF13" s="2"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
       <c r="AI13" s="3"/>
-      <c r="AU13" s="6"/>
-      <c r="AV13" s="7"/>
-      <c r="AW13" s="7"/>
-      <c r="AX13" s="7">
+      <c r="AX13">
         <v>7</v>
       </c>
-      <c r="AY13" s="7"/>
-      <c r="AZ13" s="7">
-        <v>3</v>
-      </c>
-      <c r="BA13" s="7"/>
-      <c r="BB13" s="7">
+      <c r="AZ13">
+        <v>3</v>
+      </c>
+      <c r="BB13">
         <v>-2</v>
       </c>
-      <c r="BC13" s="6"/>
-      <c r="BD13" s="6"/>
-      <c r="BE13" s="6"/>
-      <c r="BF13" s="6"/>
-      <c r="BG13" s="6"/>
-      <c r="BH13" s="6"/>
-      <c r="BI13" s="7">
+      <c r="BI13">
         <v>7</v>
       </c>
-      <c r="BJ13" s="7"/>
-      <c r="BK13" s="7">
-        <v>3</v>
-      </c>
-      <c r="BL13" s="7"/>
-      <c r="BM13" s="7">
+      <c r="BK13">
+        <v>3</v>
+      </c>
+      <c r="BM13">
         <v>-3</v>
       </c>
       <c r="BO13">
         <v>1</v>
       </c>
-      <c r="CC13" s="14"/>
-      <c r="CD13" s="8"/>
-    </row>
-    <row r="14" spans="29:85" ht="15.75" thickTop="1" thickBot="1">
-      <c r="AU14" s="6"/>
-      <c r="AV14" s="7"/>
-      <c r="AW14" s="7"/>
-      <c r="AX14" s="7"/>
-      <c r="AY14" s="7"/>
-      <c r="AZ14" s="7"/>
-      <c r="BA14" s="7"/>
-      <c r="BB14" s="6"/>
-      <c r="BC14" s="6"/>
-      <c r="BD14" s="6"/>
-      <c r="BE14" s="6"/>
-      <c r="BF14" s="6"/>
-      <c r="BG14" s="6"/>
-      <c r="BH14" s="6"/>
-      <c r="BI14" s="7">
+      <c r="BR13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="11"/>
+      <c r="Q14">
+        <v>7</v>
+      </c>
+      <c r="BI14">
         <v>8</v>
       </c>
-      <c r="BJ14" s="6"/>
-      <c r="BK14" s="7">
+      <c r="BK14">
         <v>-2</v>
       </c>
-      <c r="BL14" s="7"/>
-      <c r="BM14" s="6">
+      <c r="BM14">
         <v>3</v>
       </c>
       <c r="BO14">
         <v>-1</v>
       </c>
-      <c r="CB14" s="8"/>
-      <c r="CC14" s="12"/>
-      <c r="CD14" s="12"/>
-      <c r="CE14" s="9"/>
-      <c r="CF14" s="9"/>
-      <c r="CG14" s="13"/>
-    </row>
-    <row r="15" spans="29:85" ht="15" thickTop="1">
-      <c r="AU15" s="6"/>
-      <c r="AV15" s="7"/>
-      <c r="AW15" s="7"/>
-      <c r="AX15" s="7"/>
-      <c r="AY15" s="7"/>
-      <c r="AZ15" s="7"/>
-      <c r="BA15" s="7"/>
-      <c r="BB15" s="6"/>
-      <c r="BC15" s="6"/>
-      <c r="BD15" s="6"/>
-      <c r="BE15" s="6"/>
-      <c r="BF15" s="6"/>
-      <c r="BG15" s="6"/>
-      <c r="BH15" s="6"/>
-      <c r="BI15" s="7">
+      <c r="BR14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="10:74" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="BI15">
         <v>9</v>
       </c>
-      <c r="BJ15" s="6"/>
-      <c r="BK15" s="7">
-        <v>3</v>
-      </c>
-      <c r="BL15" s="7"/>
-      <c r="BM15" s="6">
+      <c r="BK15">
+        <v>3</v>
+      </c>
+      <c r="BM15">
         <v>3</v>
       </c>
       <c r="BO15">
         <v>-1</v>
       </c>
-      <c r="CB15" s="6"/>
-      <c r="CC15" s="6"/>
-      <c r="CD15" s="6"/>
-      <c r="CE15" s="6"/>
-      <c r="CF15" s="6"/>
-      <c r="CG15" s="6"/>
-    </row>
-    <row r="16" spans="29:85" ht="15" thickBot="1">
+      <c r="BR15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AC16">
         <v>0</v>
       </c>
       <c r="AI16">
         <v>1</v>
       </c>
-      <c r="AU16" s="6"/>
-      <c r="AV16" s="6"/>
-      <c r="AW16" s="6"/>
-      <c r="AX16" s="7"/>
-      <c r="AY16" s="6"/>
-      <c r="AZ16" s="6"/>
-      <c r="BA16" s="6"/>
-      <c r="BB16" s="6"/>
-      <c r="BC16" s="6"/>
-      <c r="BD16" s="6"/>
-      <c r="BE16" s="6"/>
-      <c r="BF16" s="6"/>
-      <c r="BG16" s="6"/>
-      <c r="BH16" s="6"/>
-      <c r="BI16" s="7">
+      <c r="BI16">
         <v>10</v>
       </c>
-      <c r="BJ16" s="6"/>
-      <c r="BK16" s="7">
+      <c r="BK16">
         <v>-3</v>
       </c>
-      <c r="BL16" s="7"/>
-      <c r="BM16" s="6">
+      <c r="BM16">
         <v>2</v>
       </c>
       <c r="BO16">
         <v>-1</v>
       </c>
-    </row>
-    <row r="17" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
+      <c r="BR16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AB17">
         <v>2</v>
       </c>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="18"/>
-      <c r="AU17" s="6"/>
-      <c r="AV17" s="6"/>
-      <c r="AW17" s="6"/>
-      <c r="AX17" s="7"/>
-      <c r="AY17" s="6"/>
-      <c r="AZ17" s="6"/>
-      <c r="BA17" s="6"/>
-      <c r="BB17" s="6"/>
-      <c r="BC17" s="6"/>
-      <c r="BD17" s="6"/>
-      <c r="BE17" s="6"/>
-      <c r="BF17" s="6"/>
-      <c r="BG17" s="6"/>
-      <c r="BH17" s="6"/>
-      <c r="BI17" s="7">
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="16"/>
+      <c r="BI17">
         <v>11</v>
       </c>
-      <c r="BJ17" s="6"/>
-      <c r="BK17" s="7">
-        <v>1</v>
-      </c>
-      <c r="BL17" s="7"/>
-      <c r="BM17" s="7">
+      <c r="BK17">
+        <v>1</v>
+      </c>
+      <c r="BM17">
         <v>2</v>
       </c>
       <c r="BO17">
         <v>-1</v>
       </c>
-    </row>
-    <row r="18" spans="24:87" ht="15" thickTop="1">
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19">
-        <v>3</v>
-      </c>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="19"/>
-      <c r="AU18" s="6"/>
-      <c r="AV18" s="6"/>
-      <c r="AW18" s="6"/>
-      <c r="AX18" s="7"/>
-      <c r="AY18" s="6"/>
-      <c r="AZ18" s="6"/>
-      <c r="BA18" s="6"/>
-      <c r="BB18" s="6"/>
-      <c r="BC18" s="6"/>
-      <c r="BD18" s="6"/>
-      <c r="BE18" s="6"/>
-      <c r="BF18" s="6"/>
-      <c r="BG18" s="6"/>
-      <c r="BH18" s="6"/>
-      <c r="BI18" s="7">
+      <c r="BR17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AE18">
+        <v>3</v>
+      </c>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="BI18">
         <v>12</v>
       </c>
-      <c r="BJ18" s="6"/>
-      <c r="BK18" s="7">
+      <c r="BK18">
         <v>-1</v>
       </c>
-      <c r="BL18" s="7"/>
-      <c r="BM18" s="7">
+      <c r="BM18">
         <v>-2</v>
       </c>
       <c r="BO18">
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="24:87">
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
-      <c r="AE19" s="20"/>
-      <c r="AF19" s="20"/>
-      <c r="AG19" s="19"/>
-      <c r="AH19" s="19"/>
-      <c r="AU19" s="6"/>
-      <c r="AV19" s="6"/>
-      <c r="AW19" s="6"/>
-      <c r="AX19" s="7"/>
-      <c r="AY19" s="6"/>
-      <c r="AZ19" s="6"/>
-      <c r="BA19" s="6"/>
-      <c r="BB19" s="6"/>
-      <c r="BC19" s="6"/>
-      <c r="BD19" s="6"/>
-      <c r="BE19" s="6"/>
-      <c r="BF19" s="6"/>
-      <c r="BG19" s="6"/>
-      <c r="BH19" s="6"/>
-      <c r="BI19" s="7">
+      <c r="BR18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="6"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="9"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="BI19">
         <v>13</v>
       </c>
-      <c r="BJ19" s="6"/>
-      <c r="BK19" s="7">
+      <c r="BK19">
         <v>2</v>
       </c>
-      <c r="BL19" s="7"/>
-      <c r="BM19" s="7">
+      <c r="BM19">
         <v>-2</v>
       </c>
       <c r="BO19">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="24:87" ht="15" thickBot="1">
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="19">
+      <c r="BR19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20">
         <v>4</v>
       </c>
-      <c r="AG20" s="19"/>
-      <c r="AH20" s="19">
+      <c r="AH20">
         <v>5</v>
       </c>
-      <c r="AX20" s="7"/>
-      <c r="BI20" s="7">
+      <c r="BI20">
         <v>14</v>
       </c>
-      <c r="BK20" s="7">
+      <c r="BK20">
         <v>-3</v>
       </c>
-      <c r="BL20" s="7"/>
-      <c r="BM20" s="7">
+      <c r="BM20">
         <v>-3</v>
       </c>
       <c r="BO20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
+      <c r="BR20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
       <c r="AB21">
         <v>6</v>
       </c>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="16"/>
-      <c r="AH21" s="22"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
+      <c r="AF21" s="14"/>
+      <c r="AG21" s="14"/>
+      <c r="AH21" s="19"/>
       <c r="AI21">
         <v>7</v>
       </c>
-      <c r="AX21" s="7"/>
-      <c r="BI21" s="7">
+      <c r="BI21">
         <v>15</v>
       </c>
-      <c r="BK21" s="7">
-        <v>3</v>
-      </c>
-      <c r="BL21" s="7"/>
-      <c r="BM21" s="7">
+      <c r="BK21">
+        <v>3</v>
+      </c>
+      <c r="BM21">
         <v>-3</v>
       </c>
       <c r="BO21">
         <v>-1</v>
       </c>
-    </row>
-    <row r="22" spans="24:87" ht="15" thickTop="1">
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="6"/>
-      <c r="CA22" s="6"/>
-      <c r="CB22" s="6"/>
-      <c r="CC22" s="6"/>
-      <c r="CD22" s="6"/>
-      <c r="CE22" s="6"/>
-      <c r="CF22" s="6"/>
-      <c r="CG22" s="6"/>
-      <c r="CH22" s="6"/>
-    </row>
-    <row r="23" spans="24:87" ht="15" thickBot="1">
+      <c r="BR21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="12"/>
+      <c r="N22" s="6"/>
+      <c r="BR22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="6"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="11"/>
       <c r="Y23" t="s">
         <v>2</v>
       </c>
       <c r="AU23" t="s">
         <v>3</v>
       </c>
-      <c r="CC23">
-        <v>0</v>
-      </c>
-      <c r="CI23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
-      <c r="X24" s="7">
+      <c r="BR23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="12:70" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="X24">
         <v>0</v>
       </c>
       <c r="Z24">
@@ -1934,12 +1886,15 @@
       <c r="AB24">
         <v>3</v>
       </c>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="6"/>
+      <c r="AF24">
+        <v>2</v>
+      </c>
+      <c r="AG24">
+        <v>6</v>
+      </c>
+      <c r="AH24">
+        <v>7</v>
+      </c>
       <c r="AT24">
         <v>6</v>
       </c>
@@ -1952,18 +1907,21 @@
       <c r="AX24">
         <v>10</v>
       </c>
-      <c r="CB24">
-        <v>2</v>
-      </c>
-      <c r="CC24" s="8"/>
-      <c r="CD24" s="9"/>
-      <c r="CE24" s="9"/>
-      <c r="CF24" s="9"/>
-      <c r="CG24" s="10"/>
-      <c r="CH24" s="11"/>
-    </row>
-    <row r="25" spans="24:87" ht="15" thickTop="1">
-      <c r="X25" s="7">
+      <c r="BB24">
+        <v>1</v>
+      </c>
+      <c r="BC24">
+        <v>4</v>
+      </c>
+      <c r="BD24">
+        <v>5</v>
+      </c>
+      <c r="BR24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X25">
         <v>1</v>
       </c>
       <c r="Z25">
@@ -1975,6 +1933,15 @@
       <c r="AB25">
         <v>1</v>
       </c>
+      <c r="AF25">
+        <v>2</v>
+      </c>
+      <c r="AG25">
+        <v>7</v>
+      </c>
+      <c r="AH25">
+        <v>3</v>
+      </c>
       <c r="AT25">
         <v>7</v>
       </c>
@@ -1987,14 +1954,21 @@
       <c r="AX25">
         <v>11</v>
       </c>
-      <c r="CE25">
-        <v>3</v>
-      </c>
-      <c r="CF25" s="14"/>
-      <c r="CG25" s="14"/>
-    </row>
-    <row r="26" spans="24:87">
-      <c r="X26" s="7">
+      <c r="BB25">
+        <v>1</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>4</v>
+      </c>
+      <c r="BR25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X26">
         <v>2</v>
       </c>
       <c r="Z26">
@@ -2006,6 +1980,15 @@
       <c r="AB26">
         <v>4</v>
       </c>
+      <c r="AF26">
+        <v>3</v>
+      </c>
+      <c r="AG26">
+        <v>7</v>
+      </c>
+      <c r="AH26">
+        <v>10</v>
+      </c>
       <c r="AT26">
         <v>8</v>
       </c>
@@ -2018,11 +2001,21 @@
       <c r="AX26">
         <v>11</v>
       </c>
-      <c r="CE26" s="14"/>
-      <c r="CF26" s="14"/>
-    </row>
-    <row r="27" spans="24:87" ht="15" thickBot="1">
-      <c r="X27" s="7">
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>9</v>
+      </c>
+      <c r="BD26">
+        <v>4</v>
+      </c>
+      <c r="BR26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X27">
         <v>3</v>
       </c>
       <c r="Z27">
@@ -2034,6 +2027,15 @@
       <c r="AB27">
         <v>4</v>
       </c>
+      <c r="AF27">
+        <v>7</v>
+      </c>
+      <c r="AG27">
+        <v>14</v>
+      </c>
+      <c r="AH27">
+        <v>10</v>
+      </c>
       <c r="AT27">
         <v>9</v>
       </c>
@@ -2046,17 +2048,21 @@
       <c r="AX27">
         <v>14</v>
       </c>
-      <c r="CD27" s="14"/>
-      <c r="CE27" s="8"/>
-      <c r="CF27">
+      <c r="BB27">
         <v>4</v>
       </c>
-      <c r="CH27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="24:87" ht="15.75" thickTop="1" thickBot="1">
-      <c r="X28" s="7">
+      <c r="BC27">
+        <v>9</v>
+      </c>
+      <c r="BD27">
+        <v>13</v>
+      </c>
+      <c r="BR27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X28">
         <v>4</v>
       </c>
       <c r="Z28">
@@ -2068,6 +2074,15 @@
       <c r="AB28">
         <v>7</v>
       </c>
+      <c r="AF28">
+        <v>10</v>
+      </c>
+      <c r="AG28">
+        <v>14</v>
+      </c>
+      <c r="AH28">
+        <v>15</v>
+      </c>
       <c r="AT28">
         <v>10</v>
       </c>
@@ -2080,21 +2095,21 @@
       <c r="AX28">
         <v>14</v>
       </c>
-      <c r="CB28">
-        <v>6</v>
-      </c>
-      <c r="CC28" s="8"/>
-      <c r="CD28" s="12"/>
-      <c r="CE28" s="12"/>
-      <c r="CF28" s="9"/>
-      <c r="CG28" s="9"/>
-      <c r="CH28" s="13"/>
-      <c r="CI28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="24:87" ht="15" thickTop="1">
-      <c r="X29" s="7">
+      <c r="BB28">
+        <v>9</v>
+      </c>
+      <c r="BC28">
+        <v>12</v>
+      </c>
+      <c r="BD28">
+        <v>13</v>
+      </c>
+      <c r="BR28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X29">
         <v>5</v>
       </c>
       <c r="Z29">
@@ -2106,6 +2121,15 @@
       <c r="AB29">
         <v>5</v>
       </c>
+      <c r="AF29">
+        <v>10</v>
+      </c>
+      <c r="AG29">
+        <v>15</v>
+      </c>
+      <c r="AH29">
+        <v>11</v>
+      </c>
       <c r="AT29">
         <v>11</v>
       </c>
@@ -2118,18 +2142,148 @@
       <c r="AX29">
         <v>15</v>
       </c>
-      <c r="CC29" s="6"/>
-      <c r="CD29" s="6"/>
-      <c r="CE29" s="6"/>
-      <c r="CF29" s="6"/>
-      <c r="CG29" s="6"/>
-      <c r="CH29" s="6"/>
-    </row>
-    <row r="30" spans="24:87">
-      <c r="X30" s="7"/>
-    </row>
-    <row r="31" spans="24:87">
-      <c r="X31" s="7"/>
+      <c r="BB29">
+        <v>9</v>
+      </c>
+      <c r="BC29">
+        <v>8</v>
+      </c>
+      <c r="BD29">
+        <v>12</v>
+      </c>
+      <c r="BR29">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BR30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="X31" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>14</v>
+      </c>
+      <c r="BR31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BR32">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="24:70" x14ac:dyDescent="0.25">
+      <c r="X33">
+        <v>12</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+      <c r="AA33">
+        <v>14</v>
+      </c>
+      <c r="AB33">
+        <v>15</v>
+      </c>
+      <c r="AF33">
+        <v>14</v>
+      </c>
+      <c r="AH33">
+        <v>9</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>1</v>
+      </c>
+      <c r="AM33">
+        <v>16</v>
+      </c>
+      <c r="AO33">
+        <v>1</v>
+      </c>
+      <c r="AP33">
+        <v>4</v>
+      </c>
+      <c r="AQ33">
+        <v>12</v>
+      </c>
+      <c r="AU33">
+        <v>18</v>
+      </c>
+      <c r="AW33">
+        <v>3</v>
+      </c>
+      <c r="AX33">
+        <v>6</v>
+      </c>
+      <c r="AY33">
+        <v>14</v>
+      </c>
+      <c r="BR33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="24:70" x14ac:dyDescent="0.25">
+      <c r="X34">
+        <v>13</v>
+      </c>
+      <c r="Z34">
+        <v>6</v>
+      </c>
+      <c r="AA34">
+        <v>15</v>
+      </c>
+      <c r="AB34">
+        <v>7</v>
+      </c>
+      <c r="AF34">
+        <v>15</v>
+      </c>
+      <c r="AH34">
+        <v>9</v>
+      </c>
+      <c r="AI34">
+        <v>1</v>
+      </c>
+      <c r="AJ34">
+        <v>8</v>
+      </c>
+      <c r="AM34">
+        <v>17</v>
+      </c>
+      <c r="AO34">
+        <v>1</v>
+      </c>
+      <c r="AP34">
+        <v>12</v>
+      </c>
+      <c r="AQ34">
+        <v>9</v>
+      </c>
+      <c r="AU34">
+        <v>19</v>
+      </c>
+      <c r="AW34">
+        <v>3</v>
+      </c>
+      <c r="AX34">
+        <v>14</v>
+      </c>
+      <c r="AY34">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Letter Z Model data.xlsx
+++ b/Letter Z Model data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\let\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\ner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913B356B-E4C9-4A02-9F52-C32D2203274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EFE3E8-3239-43E9-8585-E164D25511FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Y</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>Side Front Face</t>
+  </si>
+  <si>
+    <t>Bottom Cover Face</t>
+  </si>
+  <si>
+    <t>Top Cover Face</t>
+  </si>
+  <si>
+    <t>Top Font Face</t>
+  </si>
+  <si>
+    <t>Bottom Front Face</t>
   </si>
 </sst>
 </file>
@@ -315,8 +327,8 @@
       <xdr:rowOff>95160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>299</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>194104</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95520</xdr:rowOff>
     </xdr:to>
@@ -381,7 +393,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>36659</xdr:colOff>
+      <xdr:colOff>7307</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>114372</xdr:rowOff>
     </xdr:to>
@@ -446,7 +458,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>33779</xdr:colOff>
+      <xdr:colOff>4427</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>134172</xdr:rowOff>
     </xdr:to>
@@ -691,7 +703,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>52</xdr:col>
-      <xdr:colOff>87474</xdr:colOff>
+      <xdr:colOff>38877</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>194183</xdr:rowOff>
     </xdr:to>
@@ -728,16 +740,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>103997</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>105552</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>139721</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>126536</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>35723</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>77940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -760,7 +772,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1095375" y="5062440"/>
+          <a:off x="0" y="4819456"/>
           <a:ext cx="1853249" cy="2159249"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -778,8 +790,8 @@
       <xdr:rowOff>58316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>72</xdr:col>
-      <xdr:colOff>113328</xdr:colOff>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>86</xdr:row>
       <xdr:rowOff>55784</xdr:rowOff>
     </xdr:to>
@@ -1305,9 +1317,17 @@
   <dimension ref="J4:BV34"/>
   <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="15" max="15" width="3.140625" customWidth="1"/>
+    <col min="16" max="16" width="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1"/>
+    <col min="21" max="21" width="3.140625" customWidth="1"/>
     <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3" customWidth="1"/>
     <col min="32" max="34" width="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="3" customWidth="1"/>
+    <col min="38" max="38" width="3" customWidth="1"/>
     <col min="39" max="39" width="3" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="3" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="2.85546875" bestFit="1" customWidth="1"/>
@@ -1315,8 +1335,14 @@
     <col min="48" max="49" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
     <col min="51" max="51" width="3" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="3.140625" customWidth="1"/>
     <col min="54" max="56" width="2.85546875" customWidth="1"/>
+    <col min="57" max="60" width="3" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="3.140625" customWidth="1"/>
+    <col min="63" max="63" width="3" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="3" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="3.28515625" customWidth="1"/>
+    <col min="67" max="67" width="3" bestFit="1" customWidth="1"/>
     <col min="69" max="70" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="74" max="74" width="4.140625" bestFit="1" customWidth="1"/>
@@ -2161,17 +2187,29 @@
       </c>
     </row>
     <row r="31" spans="12:70" x14ac:dyDescent="0.25">
-      <c r="X31" t="s">
+      <c r="M31" t="s">
         <v>11</v>
       </c>
-      <c r="AG31" t="s">
+      <c r="V31" t="s">
         <v>12</v>
       </c>
-      <c r="AM31" t="s">
+      <c r="AB31" t="s">
         <v>13</v>
       </c>
-      <c r="AU31" t="s">
+      <c r="AJ31" t="s">
         <v>14</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>15</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD31" t="s">
+        <v>17</v>
+      </c>
+      <c r="BK31" t="s">
+        <v>18</v>
       </c>
       <c r="BR31">
         <v>25</v>
@@ -2182,107 +2220,203 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="24:70" x14ac:dyDescent="0.25">
+    <row r="33" spans="13:70" x14ac:dyDescent="0.25">
+      <c r="M33">
+        <v>12</v>
+      </c>
+      <c r="O33">
+        <v>6</v>
+      </c>
+      <c r="P33">
+        <v>14</v>
+      </c>
+      <c r="Q33">
+        <v>15</v>
+      </c>
+      <c r="U33">
+        <v>14</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
       <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>8</v>
+      </c>
+      <c r="AB33">
+        <v>16</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
+      </c>
+      <c r="AE33">
+        <v>4</v>
+      </c>
+      <c r="AF33">
         <v>12</v>
       </c>
-      <c r="Z33">
+      <c r="AJ33">
+        <v>18</v>
+      </c>
+      <c r="AL33">
+        <v>11</v>
+      </c>
+      <c r="AM33">
+        <v>14</v>
+      </c>
+      <c r="AN33">
         <v>6</v>
       </c>
-      <c r="AA33">
-        <v>14</v>
-      </c>
-      <c r="AB33">
+      <c r="AQ33">
+        <v>20</v>
+      </c>
+      <c r="AS33">
+        <v>2</v>
+      </c>
+      <c r="AT33">
+        <v>10</v>
+      </c>
+      <c r="AU33">
+        <v>11</v>
+      </c>
+      <c r="AX33">
+        <v>22</v>
+      </c>
+      <c r="AZ33">
+        <v>12</v>
+      </c>
+      <c r="BA33">
+        <v>4</v>
+      </c>
+      <c r="BB33">
+        <v>5</v>
+      </c>
+      <c r="BD33">
+        <v>24</v>
+      </c>
+      <c r="BF33">
+        <v>8</v>
+      </c>
+      <c r="BG33">
+        <v>10</v>
+      </c>
+      <c r="BH33">
+        <v>2</v>
+      </c>
+      <c r="BK33">
+        <v>26</v>
+      </c>
+      <c r="BM33">
+        <v>5</v>
+      </c>
+      <c r="BN33">
+        <v>7</v>
+      </c>
+      <c r="BO33">
         <v>15</v>
-      </c>
-      <c r="AF33">
-        <v>14</v>
-      </c>
-      <c r="AH33">
-        <v>9</v>
-      </c>
-      <c r="AI33">
-        <v>0</v>
-      </c>
-      <c r="AJ33">
-        <v>1</v>
-      </c>
-      <c r="AM33">
-        <v>16</v>
-      </c>
-      <c r="AO33">
-        <v>1</v>
-      </c>
-      <c r="AP33">
-        <v>4</v>
-      </c>
-      <c r="AQ33">
-        <v>12</v>
-      </c>
-      <c r="AU33">
-        <v>18</v>
-      </c>
-      <c r="AW33">
-        <v>3</v>
-      </c>
-      <c r="AX33">
-        <v>6</v>
-      </c>
-      <c r="AY33">
-        <v>14</v>
       </c>
       <c r="BR33">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="24:70" x14ac:dyDescent="0.25">
+    <row r="34" spans="13:70" x14ac:dyDescent="0.25">
+      <c r="M34">
+        <v>13</v>
+      </c>
+      <c r="O34">
+        <v>6</v>
+      </c>
+      <c r="P34">
+        <v>15</v>
+      </c>
+      <c r="Q34">
+        <v>7</v>
+      </c>
+      <c r="U34">
+        <v>15</v>
+      </c>
+      <c r="W34">
+        <v>8</v>
+      </c>
       <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>9</v>
+      </c>
+      <c r="AB34">
+        <v>17</v>
+      </c>
+      <c r="AD34">
+        <v>1</v>
+      </c>
+      <c r="AE34">
+        <v>12</v>
+      </c>
+      <c r="AF34">
+        <v>9</v>
+      </c>
+      <c r="AJ34">
+        <v>19</v>
+      </c>
+      <c r="AL34">
+        <v>11</v>
+      </c>
+      <c r="AM34">
+        <v>6</v>
+      </c>
+      <c r="AN34">
+        <v>3</v>
+      </c>
+      <c r="AQ34">
+        <v>21</v>
+      </c>
+      <c r="AS34">
+        <v>2</v>
+      </c>
+      <c r="AT34">
+        <v>11</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AX34">
+        <v>23</v>
+      </c>
+      <c r="AZ34">
+        <v>12</v>
+      </c>
+      <c r="BA34">
+        <v>5</v>
+      </c>
+      <c r="BB34">
         <v>13</v>
       </c>
-      <c r="Z34">
-        <v>6</v>
-      </c>
-      <c r="AA34">
+      <c r="BD34">
+        <v>25</v>
+      </c>
+      <c r="BF34">
+        <v>8</v>
+      </c>
+      <c r="BG34">
+        <v>2</v>
+      </c>
+      <c r="BH34">
+        <v>0</v>
+      </c>
+      <c r="BK34">
+        <v>27</v>
+      </c>
+      <c r="BM34">
+        <v>5</v>
+      </c>
+      <c r="BN34">
         <v>15</v>
       </c>
-      <c r="AB34">
-        <v>7</v>
-      </c>
-      <c r="AF34">
-        <v>15</v>
-      </c>
-      <c r="AH34">
-        <v>9</v>
-      </c>
-      <c r="AI34">
-        <v>1</v>
-      </c>
-      <c r="AJ34">
-        <v>8</v>
-      </c>
-      <c r="AM34">
-        <v>17</v>
-      </c>
-      <c r="AO34">
-        <v>1</v>
-      </c>
-      <c r="AP34">
-        <v>12</v>
-      </c>
-      <c r="AQ34">
-        <v>9</v>
-      </c>
-      <c r="AU34">
-        <v>19</v>
-      </c>
-      <c r="AW34">
-        <v>3</v>
-      </c>
-      <c r="AX34">
-        <v>14</v>
-      </c>
-      <c r="AY34">
-        <v>11</v>
+      <c r="BO34">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Letter Z Model data.xlsx
+++ b/Letter Z Model data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\ner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\jadd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EFE3E8-3239-43E9-8585-E164D25511FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F6EDBD-BF97-471D-8FA3-099347E86ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -881,7 +881,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'2'0'0,"0"2"0,2 2 0,2-1 0,1 3 0,-1-1 0,2 0 0,1 1 0,0-1 0,0 3 0,-1-2 0,1 0 0,-2 0 0,0 0 0,1-2 0,-1 2 0,-3 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'4'0'0,"-1"2"0,4 2 0,4-1 0,2 3 0,-2-1 0,3 0 0,2 1 0,0-1 0,0 3 0,-1-2 0,1 0 0,-4 0 0,1 0 0,1-2 0,-1 2 0,-6 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -909,7 +909,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">104 0 24575,'0'5'0,"0"0"0,0 0 0,0 0 0,-1 0 0,0-1 0,1 1 0,-2 0 0,2 0 0,-2-1 0,1 1 0,0-1 0,-1 1 0,-2 3 0,-1 1 0,0-1 0,0 0 0,0-1 0,-9 9 0,-2 4 0,5-5 1,-11 13-1367,15-24-5460</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">193 0 24575,'0'5'0,"0"0"0,0 0 0,0 0 0,-2 0 0,0-1 0,2 1 0,-3 0 0,3 0 0,-4-1 0,2 1 0,0-1 0,-1 1 0,-5 3 0,-1 1 0,0-1 0,-1 0 0,1-1 0,-17 9 0,-4 4 0,10-5 1,-21 13-1367,28-24-5460</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1315,13 +1315,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BC2F73-FC1F-461C-AE64-7E2CBDBF257A}">
   <dimension ref="J4:BV34"/>
-  <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="15" max="15" width="3.140625" customWidth="1"/>
+    <col min="15" max="15" width="3.125" customWidth="1"/>
     <col min="16" max="16" width="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.28515625" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" customWidth="1"/>
+    <col min="17" max="17" width="4.25" customWidth="1"/>
+    <col min="21" max="21" width="3.125" customWidth="1"/>
     <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="3" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" customWidth="1"/>
@@ -1330,26 +1330,26 @@
     <col min="38" max="38" width="3" customWidth="1"/>
     <col min="39" max="39" width="3" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="3" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="2.875" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="2.875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
     <col min="51" max="51" width="3" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="3.140625" customWidth="1"/>
-    <col min="54" max="56" width="2.85546875" customWidth="1"/>
+    <col min="52" max="52" width="3.125" customWidth="1"/>
+    <col min="54" max="56" width="2.875" customWidth="1"/>
     <col min="57" max="60" width="3" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="3.140625" customWidth="1"/>
+    <col min="61" max="61" width="3.125" customWidth="1"/>
     <col min="63" max="63" width="3" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="3" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="3.28515625" customWidth="1"/>
+    <col min="66" max="66" width="3.25" customWidth="1"/>
     <col min="67" max="67" width="3" bestFit="1" customWidth="1"/>
-    <col min="69" max="70" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="4" spans="10:74">
       <c r="AX4" t="s">
         <v>4</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="10:74" ht="15" thickBot="1">
       <c r="AZ5" t="s">
         <v>1</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="10:74" ht="15" thickBot="1">
       <c r="AD6" s="1"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
@@ -1421,7 +1421,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="10:74" ht="15" thickBot="1">
       <c r="AI7" s="5"/>
       <c r="AX7">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="10:74" ht="15" thickBot="1">
       <c r="AH8" s="5"/>
       <c r="AX8">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="10:74" ht="15" thickBot="1">
       <c r="K9">
         <v>0</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="J10">
         <v>2</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="M11">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="10:74" ht="15" thickBot="1">
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="AD12" s="4"/>
@@ -1634,8 +1634,14 @@
       <c r="BR12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT12">
+        <v>507</v>
+      </c>
+      <c r="BV12">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="10:74" ht="15" thickBot="1">
       <c r="L13" s="12"/>
       <c r="M13" s="6"/>
       <c r="N13">
@@ -1674,8 +1680,14 @@
       <c r="BR13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT13">
+        <v>699</v>
+      </c>
+      <c r="BV13">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="J14">
         <v>6</v>
       </c>
@@ -1703,8 +1715,14 @@
       <c r="BR14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="10:74" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="BT14">
+        <v>150</v>
+      </c>
+      <c r="BV14">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="10:74" ht="15" thickTop="1">
       <c r="BI15">
         <v>9</v>
       </c>
@@ -1720,8 +1738,14 @@
       <c r="BR15">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT15">
+        <v>294</v>
+      </c>
+      <c r="BV15">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="16" spans="10:74" ht="15" thickBot="1">
       <c r="AC16">
         <v>0</v>
       </c>
@@ -1743,8 +1767,14 @@
       <c r="BR16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT16">
+        <v>608</v>
+      </c>
+      <c r="BV16">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="AB17">
         <v>2</v>
       </c>
@@ -1769,8 +1799,14 @@
       <c r="BR17">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT17">
+        <v>754</v>
+      </c>
+      <c r="BV17">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="AE18">
         <v>3</v>
       </c>
@@ -1791,8 +1827,14 @@
       <c r="BR18">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT18">
+        <v>100</v>
+      </c>
+      <c r="BV18">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="L19" s="6"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -1816,8 +1858,14 @@
       <c r="BR19">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT19">
+        <v>396</v>
+      </c>
+      <c r="BV19">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
       <c r="AD20" s="17"/>
@@ -1843,8 +1891,14 @@
       <c r="BR20">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT20">
+        <v>507</v>
+      </c>
+      <c r="BV20">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
       <c r="AB21">
@@ -1874,15 +1928,27 @@
       <c r="BR21">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT21">
+        <v>804</v>
+      </c>
+      <c r="BV21">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="M22" s="12"/>
       <c r="N22" s="6"/>
       <c r="BR22">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="12:70" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT22">
+        <v>116</v>
+      </c>
+      <c r="BV22">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="23" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
       <c r="L23" s="6"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -1898,8 +1964,14 @@
       <c r="BR23">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="12:70" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="BT23">
+        <v>413</v>
+      </c>
+      <c r="BV23">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="12:74" ht="15" thickTop="1">
       <c r="X24">
         <v>0</v>
       </c>
@@ -1945,8 +2017,14 @@
       <c r="BR24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT24">
+        <v>117</v>
+      </c>
+      <c r="BV24">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="25" spans="12:74">
       <c r="X25">
         <v>1</v>
       </c>
@@ -1992,8 +2070,14 @@
       <c r="BR25">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT25">
+        <v>413</v>
+      </c>
+      <c r="BV25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="26" spans="12:74">
       <c r="X26">
         <v>2</v>
       </c>
@@ -2039,8 +2123,14 @@
       <c r="BR26">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT26">
+        <v>101</v>
+      </c>
+      <c r="BV26">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="27" spans="12:74">
       <c r="X27">
         <v>3</v>
       </c>
@@ -2086,8 +2176,14 @@
       <c r="BR27">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT27">
+        <v>412</v>
+      </c>
+      <c r="BV27">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="28" spans="12:74">
       <c r="X28">
         <v>4</v>
       </c>
@@ -2133,8 +2229,14 @@
       <c r="BR28">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT28">
+        <v>101</v>
+      </c>
+      <c r="BV28">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="29" spans="12:74">
       <c r="X29">
         <v>5</v>
       </c>
@@ -2180,13 +2282,25 @@
       <c r="BR29">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT29">
+        <v>412</v>
+      </c>
+      <c r="BV29">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="30" spans="12:74">
       <c r="BR30">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT30">
+        <v>272</v>
+      </c>
+      <c r="BV30">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="31" spans="12:74">
       <c r="M31" t="s">
         <v>11</v>
       </c>
@@ -2214,13 +2328,25 @@
       <c r="BR31">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="12:70" x14ac:dyDescent="0.25">
+      <c r="BT31">
+        <v>409</v>
+      </c>
+      <c r="BV31">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="32" spans="12:74">
       <c r="BR32">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="13:70" x14ac:dyDescent="0.25">
+      <c r="BT32">
+        <v>272</v>
+      </c>
+      <c r="BV32">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="33" spans="13:74">
       <c r="M33">
         <v>12</v>
       </c>
@@ -2320,8 +2446,14 @@
       <c r="BR33">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="13:70" x14ac:dyDescent="0.25">
+      <c r="BT33">
+        <v>409</v>
+      </c>
+      <c r="BV33">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="34" spans="13:74">
       <c r="M34">
         <v>13</v>
       </c>

--- a/Letter Z Model data.xlsx
+++ b/Letter Z Model data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\jadd\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StudentRaniWheeza(TL\Desktop\ere\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F6EDBD-BF97-471D-8FA3-099347E86ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E092B5FD-9571-4FD8-9FD9-A9D61A757051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{87AB4E44-0602-4CBF-A180-22F6667C61E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -102,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -881,7 +881,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'4'0'0,"-1"2"0,4 2 0,4-1 0,2 3 0,-2-1 0,3 0 0,2 1 0,0-1 0,0 3 0,-1-2 0,1 0 0,-4 0 0,1 0 0,1-2 0,-1 2 0,-6 0-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'2'0'0,"0"2"0,2 2 0,3-1 0,1 3 0,-1-1 0,1 0 0,2 1 0,-1-1 0,1 3 0,-1-2 0,1 0 0,-3 0 0,1 0 0,0-2 0,0 2 0,-4 0-8191</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -909,7 +909,7 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">193 0 24575,'0'5'0,"0"0"0,0 0 0,0 0 0,-2 0 0,0-1 0,2 1 0,-3 0 0,3 0 0,-4-1 0,2 1 0,0-1 0,-1 1 0,-5 3 0,-1 1 0,0-1 0,-1 0 0,1-1 0,-17 9 0,-4 4 0,10-5 1,-21 13-1367,28-24-5460</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">113 0 24575,'0'5'0,"0"0"0,0 0 0,0 0 0,-1 0 0,0-1 0,1 1 0,-2 0 0,2 0 0,-2-1 0,1 1 0,0-1 0,-1 1 0,-3 3 0,0 1 0,0-1 0,-1 0 0,0-1 0,-9 9 0,-3 4 0,7-5 1,-13 13-1367,16-24-5460</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1315,13 +1315,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BC2F73-FC1F-461C-AE64-7E2CBDBF257A}">
   <dimension ref="J4:BV34"/>
-  <sheetFormatPr defaultColWidth="2.375" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="2.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="3" customWidth="1"/>
-    <col min="15" max="15" width="3.125" customWidth="1"/>
+    <col min="15" max="15" width="3.140625" customWidth="1"/>
     <col min="16" max="16" width="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.25" customWidth="1"/>
-    <col min="21" max="21" width="3.125" customWidth="1"/>
+    <col min="17" max="17" width="4.28515625" customWidth="1"/>
+    <col min="21" max="21" width="3.140625" customWidth="1"/>
     <col min="24" max="24" width="3" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="3" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" customWidth="1"/>
@@ -1330,26 +1330,26 @@
     <col min="38" max="38" width="3" customWidth="1"/>
     <col min="39" max="39" width="3" bestFit="1" customWidth="1"/>
     <col min="42" max="43" width="3" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="3" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="3" customWidth="1"/>
     <col min="51" max="51" width="3" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="3.125" customWidth="1"/>
-    <col min="54" max="56" width="2.875" customWidth="1"/>
+    <col min="52" max="52" width="3.140625" customWidth="1"/>
+    <col min="54" max="56" width="2.85546875" customWidth="1"/>
     <col min="57" max="60" width="3" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="3.125" customWidth="1"/>
+    <col min="61" max="61" width="3.140625" customWidth="1"/>
     <col min="63" max="63" width="3" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="3" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="3.25" customWidth="1"/>
+    <col min="66" max="66" width="3.28515625" customWidth="1"/>
     <col min="67" max="67" width="3" bestFit="1" customWidth="1"/>
-    <col min="69" max="70" width="2.875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="4.125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="4.125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="10:74">
+    <row r="4" spans="10:74" x14ac:dyDescent="0.25">
       <c r="AX4" t="s">
         <v>4</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="10:74" ht="15" thickBot="1">
+    <row r="5" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AZ5" t="s">
         <v>1</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="10:74" ht="15" thickBot="1">
+    <row r="6" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AD6" s="1"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
@@ -1421,7 +1421,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="10:74" ht="15" thickBot="1">
+    <row r="7" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AI7" s="5"/>
       <c r="AX7">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="10:74" ht="15" thickBot="1">
+    <row r="8" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AH8" s="5"/>
       <c r="AX8">
         <v>2</v>
@@ -1487,7 +1487,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="10:74" ht="15" thickBot="1">
+    <row r="9" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K9">
         <v>0</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="10" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J10">
         <v>2</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="11" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M11">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="10:74" ht="15" thickBot="1">
+    <row r="12" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="AD12" s="4"/>
@@ -1641,7 +1641,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="10:74" ht="15" thickBot="1">
+    <row r="13" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
       <c r="M13" s="6"/>
       <c r="N13">
@@ -1687,7 +1687,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="10:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="14" spans="10:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J14">
         <v>6</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="15" spans="10:74" ht="15" thickTop="1">
+    <row r="15" spans="10:74" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="BI15">
         <v>9</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="16" spans="10:74" ht="15" thickBot="1">
+    <row r="16" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AC16">
         <v>0</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="17" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="17" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AB17">
         <v>2</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="18" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="18" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AE18">
         <v>3</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="19" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="19" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L19" s="6"/>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
@@ -1865,7 +1865,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="20" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="20" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
       <c r="AD20" s="17"/>
@@ -1898,7 +1898,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="21" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="21" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
       <c r="AB21">
@@ -1935,7 +1935,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="22" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="22" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M22" s="12"/>
       <c r="N22" s="6"/>
       <c r="BR22">
@@ -1948,7 +1948,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="12:74" ht="15.75" thickTop="1" thickBot="1">
+    <row r="23" spans="12:74" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L23" s="6"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -1971,7 +1971,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="24" spans="12:74" ht="15" thickTop="1">
+    <row r="24" spans="12:74" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="X24">
         <v>0</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="25" spans="12:74">
+    <row r="25" spans="12:74" x14ac:dyDescent="0.25">
       <c r="X25">
         <v>1</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="26" spans="12:74">
+    <row r="26" spans="12:74" x14ac:dyDescent="0.25">
       <c r="X26">
         <v>2</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="27" spans="12:74">
+    <row r="27" spans="12:74" x14ac:dyDescent="0.25">
       <c r="X27">
         <v>3</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="28" spans="12:74">
+    <row r="28" spans="12:74" x14ac:dyDescent="0.25">
       <c r="X28">
         <v>4</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="29" spans="12:74">
+    <row r="29" spans="12:74" x14ac:dyDescent="0.25">
       <c r="X29">
         <v>5</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="30" spans="12:74">
+    <row r="30" spans="12:74" x14ac:dyDescent="0.25">
       <c r="BR30">
         <v>24</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="31" spans="12:74">
+    <row r="31" spans="12:74" x14ac:dyDescent="0.25">
       <c r="M31" t="s">
         <v>11</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="32" spans="12:74">
+    <row r="32" spans="12:74" x14ac:dyDescent="0.25">
       <c r="BR32">
         <v>26</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="33" spans="13:74">
+    <row r="33" spans="13:74" x14ac:dyDescent="0.25">
       <c r="M33">
         <v>12</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="34" spans="13:74">
+    <row r="34" spans="13:74" x14ac:dyDescent="0.25">
       <c r="M34">
         <v>13</v>
       </c>
